--- a/product-definitions/spreadsheet/liquid-water-content.xlsx
+++ b/product-definitions/spreadsheet/liquid-water-content.xlsx
@@ -1767,7 +1767,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="11" t="s">
         <v>31</v>
